--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/88.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/88.xlsx
@@ -426,13 +426,13 @@
         <v>-6.139829968485863</v>
       </c>
       <c r="E2">
-        <v>-14.39583980813136</v>
+        <v>-12.75544538359285</v>
       </c>
       <c r="F2">
-        <v>-0.1797177687544717</v>
+        <v>-0.3540783382675312</v>
       </c>
       <c r="G2">
-        <v>-12.99991427464368</v>
+        <v>-11.25529319144869</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.793779856906344</v>
       </c>
       <c r="E3">
-        <v>-14.91120279257429</v>
+        <v>-13.77869484189204</v>
       </c>
       <c r="F3">
-        <v>-0.2438690255294738</v>
+        <v>-0.3608891750533488</v>
       </c>
       <c r="G3">
-        <v>-12.16626262858103</v>
+        <v>-11.38453688930184</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.428684208587609</v>
       </c>
       <c r="E4">
-        <v>-15.00227946181655</v>
+        <v>-14.5402120879699</v>
       </c>
       <c r="F4">
-        <v>0.2027262072396153</v>
+        <v>-0.120543343335489</v>
       </c>
       <c r="G4">
-        <v>-12.76022415650936</v>
+        <v>-10.77572425408433</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.07464909695245</v>
       </c>
       <c r="E5">
-        <v>-15.5169495897363</v>
+        <v>-15.16260555558411</v>
       </c>
       <c r="F5">
-        <v>0.3547423944295609</v>
+        <v>-0.3980828714390466</v>
       </c>
       <c r="G5">
-        <v>-11.99031375425984</v>
+        <v>-11.52302031975509</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.723117708564708</v>
       </c>
       <c r="E6">
-        <v>-15.90517113793988</v>
+        <v>-15.60851986264541</v>
       </c>
       <c r="F6">
-        <v>0.4494015942822661</v>
+        <v>-0.1117187453934659</v>
       </c>
       <c r="G6">
-        <v>-11.09088818942295</v>
+        <v>-9.979597641709317</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.380695165903282</v>
       </c>
       <c r="E7">
-        <v>-17.20586208479299</v>
+        <v>-15.97401752827849</v>
       </c>
       <c r="F7">
-        <v>0.6399501195808335</v>
+        <v>-0.07191072148453284</v>
       </c>
       <c r="G7">
-        <v>-10.3486009791531</v>
+        <v>-10.15327217124502</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.043999011700655</v>
       </c>
       <c r="E8">
-        <v>-17.34728632805254</v>
+        <v>-16.48183607502463</v>
       </c>
       <c r="F8">
-        <v>0.7511062562602908</v>
+        <v>0.2167281014491353</v>
       </c>
       <c r="G8">
-        <v>-10.29676776764473</v>
+        <v>-9.527420158136882</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.71983962282132</v>
       </c>
       <c r="E9">
-        <v>-18.45991427784111</v>
+        <v>-17.96459884783015</v>
       </c>
       <c r="F9">
-        <v>0.5732441777355978</v>
+        <v>0.5461292275397615</v>
       </c>
       <c r="G9">
-        <v>-10.49354659449901</v>
+        <v>-9.41887068044972</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.403501865291515</v>
       </c>
       <c r="E10">
-        <v>-18.7857968528551</v>
+        <v>-18.36486160842011</v>
       </c>
       <c r="F10">
-        <v>1.006049578350283</v>
+        <v>0.3728952376945093</v>
       </c>
       <c r="G10">
-        <v>-9.885309994205334</v>
+        <v>-9.2394457333123</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.096622648739427</v>
       </c>
       <c r="E11">
-        <v>-19.9717634391979</v>
+        <v>-18.79366734068043</v>
       </c>
       <c r="F11">
-        <v>1.270926682334648</v>
+        <v>0.8566502037857814</v>
       </c>
       <c r="G11">
-        <v>-9.19007225713961</v>
+        <v>-8.685382900223257</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.799141556510568</v>
       </c>
       <c r="E12">
-        <v>-19.68039236459637</v>
+        <v>-18.97093898418469</v>
       </c>
       <c r="F12">
-        <v>1.621322780249227</v>
+        <v>0.8801642408816481</v>
       </c>
       <c r="G12">
-        <v>-8.72056737821463</v>
+        <v>-7.962382928265204</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.508214047938545</v>
       </c>
       <c r="E13">
-        <v>-20.74746839434179</v>
+        <v>-19.97690778567061</v>
       </c>
       <c r="F13">
-        <v>1.715175150251606</v>
+        <v>1.344018508488065</v>
       </c>
       <c r="G13">
-        <v>-8.130005780555122</v>
+        <v>-8.158936638022814</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.232527734831963</v>
       </c>
       <c r="E14">
-        <v>-21.19830968112343</v>
+        <v>-20.14761314186375</v>
       </c>
       <c r="F14">
-        <v>1.358758478053479</v>
+        <v>1.125546546408529</v>
       </c>
       <c r="G14">
-        <v>-7.86846606186162</v>
+        <v>-7.106126877260408</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.976694321008367</v>
       </c>
       <c r="E15">
-        <v>-22.16863486369497</v>
+        <v>-21.52873884404111</v>
       </c>
       <c r="F15">
-        <v>2.011432468188821</v>
+        <v>1.372110103851802</v>
       </c>
       <c r="G15">
-        <v>-7.60832670393123</v>
+        <v>-7.574234705967815</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.74882611572736</v>
       </c>
       <c r="E16">
-        <v>-23.14431270254358</v>
+        <v>-21.69914079247574</v>
       </c>
       <c r="F16">
-        <v>2.005118651844683</v>
+        <v>1.783396176076562</v>
       </c>
       <c r="G16">
-        <v>-7.464066371511948</v>
+        <v>-6.414173201369641</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.555499234066549</v>
       </c>
       <c r="E17">
-        <v>-24.65181000037899</v>
+        <v>-24.21639269606748</v>
       </c>
       <c r="F17">
-        <v>2.254818408274955</v>
+        <v>1.998261426484309</v>
       </c>
       <c r="G17">
-        <v>-7.217672398660611</v>
+        <v>-5.907226052395504</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.393253481022999</v>
       </c>
       <c r="E18">
-        <v>-23.99399480907678</v>
+        <v>-24.18929883607958</v>
       </c>
       <c r="F18">
-        <v>2.108109571034745</v>
+        <v>2.564783549993696</v>
       </c>
       <c r="G18">
-        <v>-6.920630389603965</v>
+        <v>-5.579256926910987</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.259257832584513</v>
       </c>
       <c r="E19">
-        <v>-25.93261641786443</v>
+        <v>-25.47836971862902</v>
       </c>
       <c r="F19">
-        <v>2.531960320025169</v>
+        <v>2.585908575499889</v>
       </c>
       <c r="G19">
-        <v>-6.688852475308511</v>
+        <v>-5.420416951936756</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.143221048961432</v>
       </c>
       <c r="E20">
-        <v>-25.8295211786058</v>
+        <v>-25.53055585309341</v>
       </c>
       <c r="F20">
-        <v>2.919710817601589</v>
+        <v>2.725496766545634</v>
       </c>
       <c r="G20">
-        <v>-6.324689155443141</v>
+        <v>-5.524394566234185</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.033642265139306</v>
       </c>
       <c r="E21">
-        <v>-26.42266976107848</v>
+        <v>-25.6588973349448</v>
       </c>
       <c r="F21">
-        <v>2.681874939114212</v>
+        <v>3.254056468719526</v>
       </c>
       <c r="G21">
-        <v>-6.043080909690577</v>
+        <v>-6.164786495350803</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.9219773951850611</v>
       </c>
       <c r="E22">
-        <v>-26.71352006116912</v>
+        <v>-26.74524655006686</v>
       </c>
       <c r="F22">
-        <v>3.098583504357698</v>
+        <v>3.03064909365411</v>
       </c>
       <c r="G22">
-        <v>-5.559565802043402</v>
+        <v>-5.467737889875098</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.7990820449633625</v>
       </c>
       <c r="E23">
-        <v>-26.69617147724574</v>
+        <v>-27.708837891789</v>
       </c>
       <c r="F23">
-        <v>2.856484847215514</v>
+        <v>2.649470863051501</v>
       </c>
       <c r="G23">
-        <v>-6.051946550644745</v>
+        <v>-4.940874498936706</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.6638249821560476</v>
       </c>
       <c r="E24">
-        <v>-27.69666988213039</v>
+        <v>-27.46971182181397</v>
       </c>
       <c r="F24">
-        <v>3.431226032095478</v>
+        <v>3.310587573756175</v>
       </c>
       <c r="G24">
-        <v>-6.304061146187942</v>
+        <v>-4.542920440751995</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.5198448990069481</v>
       </c>
       <c r="E25">
-        <v>-27.1469086091252</v>
+        <v>-28.43621044384903</v>
       </c>
       <c r="F25">
-        <v>3.129019379471357</v>
+        <v>3.14209598729195</v>
       </c>
       <c r="G25">
-        <v>-5.652959602251781</v>
+        <v>-5.090577368222549</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.3743384519196754</v>
       </c>
       <c r="E26">
-        <v>-28.1797312614766</v>
+        <v>-28.03441705904447</v>
       </c>
       <c r="F26">
-        <v>3.313170423318104</v>
+        <v>3.224937697776317</v>
       </c>
       <c r="G26">
-        <v>-5.829534169679889</v>
+        <v>-5.630550519496454</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.239623524692351</v>
       </c>
       <c r="E27">
-        <v>-27.87088933415349</v>
+        <v>-27.55482901926214</v>
       </c>
       <c r="F27">
-        <v>3.246667431486554</v>
+        <v>3.041330062945807</v>
       </c>
       <c r="G27">
-        <v>-6.024154520842563</v>
+        <v>-4.808078585719921</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.1284651121986506</v>
       </c>
       <c r="E28">
-        <v>-27.5711632250078</v>
+        <v>-28.09621714382715</v>
       </c>
       <c r="F28">
-        <v>3.557679629602434</v>
+        <v>3.150603320518701</v>
       </c>
       <c r="G28">
-        <v>-6.139738907800678</v>
+        <v>-5.732995351209201</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.05337621898593662</v>
       </c>
       <c r="E29">
-        <v>-27.20226467539496</v>
+        <v>-28.23352047573971</v>
       </c>
       <c r="F29">
-        <v>3.278751757731785</v>
+        <v>3.052372200425125</v>
       </c>
       <c r="G29">
-        <v>-6.013590570026749</v>
+        <v>-5.667959684090219</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.02790070603483773</v>
       </c>
       <c r="E30">
-        <v>-27.34915478678177</v>
+        <v>-28.20188455632213</v>
       </c>
       <c r="F30">
-        <v>3.38011907681236</v>
+        <v>3.324200963653782</v>
       </c>
       <c r="G30">
-        <v>-5.818404115576859</v>
+        <v>-5.63393389703759</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.06391091750384983</v>
       </c>
       <c r="E31">
-        <v>-26.61323247579526</v>
+        <v>-26.37688236038693</v>
       </c>
       <c r="F31">
-        <v>3.144564522152293</v>
+        <v>3.207937941936066</v>
       </c>
       <c r="G31">
-        <v>-6.271981959912404</v>
+        <v>-5.489157119514182</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.1685308759826862</v>
       </c>
       <c r="E32">
-        <v>-26.95967432280406</v>
+        <v>-26.76129999042405</v>
       </c>
       <c r="F32">
-        <v>2.97343707061236</v>
+        <v>3.061109819789854</v>
       </c>
       <c r="G32">
-        <v>-5.663387820700486</v>
+        <v>-5.362105002808033</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.3487085409231765</v>
       </c>
       <c r="E33">
-        <v>-26.43651330611993</v>
+        <v>-26.33491246328384</v>
       </c>
       <c r="F33">
-        <v>2.855088219774394</v>
+        <v>3.097117294054743</v>
       </c>
       <c r="G33">
-        <v>-5.964091293123566</v>
+        <v>-5.692950992366177</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.6033563218757556</v>
       </c>
       <c r="E34">
-        <v>-25.39947011599338</v>
+        <v>-26.22002507770924</v>
       </c>
       <c r="F34">
-        <v>3.243913938239649</v>
+        <v>2.964320058977148</v>
       </c>
       <c r="G34">
-        <v>-6.588218512005745</v>
+        <v>-6.072597733718719</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.927383221123078</v>
       </c>
       <c r="E35">
-        <v>-24.79242364679116</v>
+        <v>-25.71987323745808</v>
       </c>
       <c r="F35">
-        <v>3.468621850127459</v>
+        <v>3.064317258373493</v>
       </c>
       <c r="G35">
-        <v>-7.69540067270514</v>
+        <v>-5.489064424239083</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.313649790010698</v>
       </c>
       <c r="E36">
-        <v>-25.07253693500962</v>
+        <v>-24.76290705320917</v>
       </c>
       <c r="F36">
-        <v>3.245265833841017</v>
+        <v>3.184637623630122</v>
       </c>
       <c r="G36">
-        <v>-7.213547458918679</v>
+        <v>-6.553639863848058</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.744906998698931</v>
       </c>
       <c r="E37">
-        <v>-24.95146818241455</v>
+        <v>-24.5917760204593</v>
       </c>
       <c r="F37">
-        <v>3.542460863678202</v>
+        <v>3.432339357884841</v>
       </c>
       <c r="G37">
-        <v>-7.425147598152276</v>
+        <v>-6.50852043869333</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.207165395874966</v>
       </c>
       <c r="E38">
-        <v>-23.43845067476379</v>
+        <v>-23.77865228459003</v>
       </c>
       <c r="F38">
-        <v>3.769027632017894</v>
+        <v>3.403906475151151</v>
       </c>
       <c r="G38">
-        <v>-7.642882178270142</v>
+        <v>-6.022005976787576</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.680297854158512</v>
       </c>
       <c r="E39">
-        <v>-23.46179042979933</v>
+        <v>-24.26027813767581</v>
       </c>
       <c r="F39">
-        <v>3.460033336895234</v>
+        <v>3.476613938829669</v>
       </c>
       <c r="G39">
-        <v>-6.542675337021992</v>
+        <v>-5.229239568134923</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.141388588055175</v>
       </c>
       <c r="E40">
-        <v>-21.89977483338557</v>
+        <v>-23.11145862361793</v>
       </c>
       <c r="F40">
-        <v>3.617441367510002</v>
+        <v>3.346909827634128</v>
       </c>
       <c r="G40">
-        <v>-7.456001882578284</v>
+        <v>-6.76434946633159</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.573254085384709</v>
       </c>
       <c r="E41">
-        <v>-22.20360826845621</v>
+        <v>-22.76165664889544</v>
       </c>
       <c r="F41">
-        <v>3.424352239387048</v>
+        <v>3.183890436232796</v>
       </c>
       <c r="G41">
-        <v>-7.189301023389057</v>
+        <v>-6.433629277503938</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.955268049587736</v>
       </c>
       <c r="E42">
-        <v>-20.80754313052755</v>
+        <v>-22.3021976760772</v>
       </c>
       <c r="F42">
-        <v>3.069363672591348</v>
+        <v>3.231299559429818</v>
       </c>
       <c r="G42">
-        <v>-7.323868078469353</v>
+        <v>-7.062894463063066</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.275275719796923</v>
       </c>
       <c r="E43">
-        <v>-21.42914411519041</v>
+        <v>-21.3027317632663</v>
       </c>
       <c r="F43">
-        <v>3.828414947859397</v>
+        <v>3.577644940744708</v>
       </c>
       <c r="G43">
-        <v>-8.068098578970751</v>
+        <v>-6.014904856605839</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.526388658431202</v>
       </c>
       <c r="E44">
-        <v>-19.75073315135751</v>
+        <v>-22.42036820530736</v>
       </c>
       <c r="F44">
-        <v>3.388134359801848</v>
+        <v>3.380019672724024</v>
       </c>
       <c r="G44">
-        <v>-7.821843649032064</v>
+        <v>-6.736087339062832</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.70392592957807</v>
       </c>
       <c r="E45">
-        <v>-19.77919461049572</v>
+        <v>-20.30730977774425</v>
       </c>
       <c r="F45">
-        <v>3.374063711097896</v>
+        <v>3.321949461052973</v>
       </c>
       <c r="G45">
-        <v>-7.364998296249258</v>
+        <v>-6.426356008954159</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.816113463344209</v>
       </c>
       <c r="E46">
-        <v>-20.85452151988312</v>
+        <v>-20.03663835783178</v>
       </c>
       <c r="F46">
-        <v>3.461552562711968</v>
+        <v>3.333324602228216</v>
       </c>
       <c r="G46">
-        <v>-7.591171456946726</v>
+        <v>-6.055306754367105</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.871408407763355</v>
       </c>
       <c r="E47">
-        <v>-20.1839496173013</v>
+        <v>-20.38092465121294</v>
       </c>
       <c r="F47">
-        <v>3.263972026531036</v>
+        <v>3.174433793962437</v>
       </c>
       <c r="G47">
-        <v>-7.342609076767167</v>
+        <v>-6.274574117069654</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.885358652430297</v>
       </c>
       <c r="E48">
-        <v>-18.4682919547553</v>
+        <v>-19.43285691838909</v>
       </c>
       <c r="F48">
-        <v>3.04882016100192</v>
+        <v>3.331643016400533</v>
       </c>
       <c r="G48">
-        <v>-7.372625793171739</v>
+        <v>-6.341877507883037</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.87835766746889</v>
       </c>
       <c r="E49">
-        <v>-17.88660493999604</v>
+        <v>-19.25677173507484</v>
       </c>
       <c r="F49">
-        <v>2.995047519416593</v>
+        <v>3.398520430298148</v>
       </c>
       <c r="G49">
-        <v>-8.241928704146803</v>
+        <v>-6.098827186026364</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.866096993804926</v>
       </c>
       <c r="E50">
-        <v>-17.9607904011897</v>
+        <v>-18.44487521566164</v>
       </c>
       <c r="F50">
-        <v>3.344828968718295</v>
+        <v>3.160785612633913</v>
       </c>
       <c r="G50">
-        <v>-8.90985444051354</v>
+        <v>-5.967779240854314</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.872233846282437</v>
       </c>
       <c r="E51">
-        <v>-17.4528224148013</v>
+        <v>-17.79740305899295</v>
       </c>
       <c r="F51">
-        <v>3.090472130749485</v>
+        <v>3.300176652237791</v>
       </c>
       <c r="G51">
-        <v>-8.492196015279086</v>
+        <v>-6.479126104850142</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.911433830698959</v>
       </c>
       <c r="E52">
-        <v>-16.8305014027712</v>
+        <v>-17.49619613884676</v>
       </c>
       <c r="F52">
-        <v>2.915156453620998</v>
+        <v>3.020839566870158</v>
       </c>
       <c r="G52">
-        <v>-8.605122034169167</v>
+        <v>-6.589840679319988</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.996520610606037</v>
       </c>
       <c r="E53">
-        <v>-16.07024307246748</v>
+        <v>-17.8245286182989</v>
       </c>
       <c r="F53">
-        <v>2.879750374090541</v>
+        <v>3.105024889281867</v>
       </c>
       <c r="G53">
-        <v>-7.782828869851753</v>
+        <v>-5.960327202845415</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.138685046897868</v>
       </c>
       <c r="E54">
-        <v>-15.52496498872988</v>
+        <v>-16.7774231589273</v>
       </c>
       <c r="F54">
-        <v>2.94283552201814</v>
+        <v>3.27540681015928</v>
       </c>
       <c r="G54">
-        <v>-8.280059567668129</v>
+        <v>-6.626465244620945</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.337550172905742</v>
       </c>
       <c r="E55">
-        <v>-16.24560822841451</v>
+        <v>-16.71173764344604</v>
       </c>
       <c r="F55">
-        <v>2.955413452662248</v>
+        <v>2.974207452296963</v>
       </c>
       <c r="G55">
-        <v>-7.948534916274433</v>
+        <v>-6.901541784024527</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.595146487768358</v>
       </c>
       <c r="E56">
-        <v>-15.59672318785542</v>
+        <v>-16.71988889665985</v>
       </c>
       <c r="F56">
-        <v>2.720988791139599</v>
+        <v>3.268854424003136</v>
       </c>
       <c r="G56">
-        <v>-8.853621513983478</v>
+        <v>-7.272677112795602</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.902820738369241</v>
       </c>
       <c r="E57">
-        <v>-15.33407622388455</v>
+        <v>-15.27048286339484</v>
       </c>
       <c r="F57">
-        <v>2.702088760477325</v>
+        <v>2.935529321525449</v>
       </c>
       <c r="G57">
-        <v>-8.445338553716242</v>
+        <v>-6.769984014839429</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.248607652256456</v>
       </c>
       <c r="E58">
-        <v>-15.38302449943346</v>
+        <v>-14.37079734686894</v>
       </c>
       <c r="F58">
-        <v>2.925279103283208</v>
+        <v>2.671570048623386</v>
       </c>
       <c r="G58">
-        <v>-8.615285408974728</v>
+        <v>-7.12242469295024</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.622758684281131</v>
       </c>
       <c r="E59">
-        <v>-14.547946721575</v>
+        <v>-14.0406263069697</v>
       </c>
       <c r="F59">
-        <v>2.651008312951097</v>
+        <v>3.30573334077577</v>
       </c>
       <c r="G59">
-        <v>-9.11593590033317</v>
+        <v>-7.42813039968316</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.007174027228713</v>
       </c>
       <c r="E60">
-        <v>-14.2790232926295</v>
+        <v>-14.43359369593331</v>
       </c>
       <c r="F60">
-        <v>3.067324232045656</v>
+        <v>3.456307340317442</v>
       </c>
       <c r="G60">
-        <v>-9.102839382179814</v>
+        <v>-7.199921253479039</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.389715769601634</v>
       </c>
       <c r="E61">
-        <v>-15.19141570722091</v>
+        <v>-14.68426284615389</v>
       </c>
       <c r="F61">
-        <v>2.619586680628106</v>
+        <v>3.067163528769512</v>
       </c>
       <c r="G61">
-        <v>-9.147316561499922</v>
+        <v>-7.839111454564902</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.758366969343315</v>
       </c>
       <c r="E62">
-        <v>-14.83203148149819</v>
+        <v>-14.163601547122</v>
       </c>
       <c r="F62">
-        <v>2.246930693865498</v>
+        <v>3.264677795558221</v>
       </c>
       <c r="G62">
-        <v>-9.339685741695893</v>
+        <v>-7.962233953715937</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.098255008788646</v>
       </c>
       <c r="E63">
-        <v>-12.98546469233846</v>
+        <v>-15.17870880915539</v>
       </c>
       <c r="F63">
-        <v>2.533870535256024</v>
+        <v>3.381114774430525</v>
       </c>
       <c r="G63">
-        <v>-9.365372264535099</v>
+        <v>-7.993919185072301</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.406154373493703</v>
       </c>
       <c r="E64">
-        <v>-13.68616906096732</v>
+        <v>-13.08652211829363</v>
       </c>
       <c r="F64">
-        <v>2.511075521065788</v>
+        <v>2.752118838136805</v>
       </c>
       <c r="G64">
-        <v>-9.25584948645939</v>
+        <v>-8.399527224543807</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.672697301822154</v>
       </c>
       <c r="E65">
-        <v>-13.5924070066385</v>
+        <v>-13.39164163998244</v>
       </c>
       <c r="F65">
-        <v>2.37526799884642</v>
+        <v>3.157157363409651</v>
       </c>
       <c r="G65">
-        <v>-9.447953823012218</v>
+        <v>-7.483396646915753</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.894423707676204</v>
       </c>
       <c r="E66">
-        <v>-13.18583155328184</v>
+        <v>-13.65024014819046</v>
       </c>
       <c r="F66">
-        <v>2.442857808710443</v>
+        <v>2.853004047388951</v>
       </c>
       <c r="G66">
-        <v>-9.241786289008566</v>
+        <v>-8.030861562745029</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.070809627692984</v>
       </c>
       <c r="E67">
-        <v>-13.46078690960556</v>
+        <v>-14.28098865034883</v>
       </c>
       <c r="F67">
-        <v>2.364837196510368</v>
+        <v>2.867512074081581</v>
       </c>
       <c r="G67">
-        <v>-9.230441049445483</v>
+        <v>-8.048486907196109</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.197522655762803</v>
       </c>
       <c r="E68">
-        <v>-12.85018558830732</v>
+        <v>-14.42933240189209</v>
       </c>
       <c r="F68">
-        <v>2.472445435603635</v>
+        <v>2.90775084903997</v>
       </c>
       <c r="G68">
-        <v>-9.250052721220126</v>
+        <v>-7.554583307646701</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.280077998724892</v>
       </c>
       <c r="E69">
-        <v>-13.7607847271917</v>
+        <v>-13.90373959466584</v>
       </c>
       <c r="F69">
-        <v>2.293148624737294</v>
+        <v>2.683912722925099</v>
       </c>
       <c r="G69">
-        <v>-7.995922065123561</v>
+        <v>-8.816841353042177</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.316750181073918</v>
       </c>
       <c r="E70">
-        <v>-14.11597105750932</v>
+        <v>-13.30425567705643</v>
       </c>
       <c r="F70">
-        <v>2.29114728909213</v>
+        <v>2.762557924146884</v>
       </c>
       <c r="G70">
-        <v>-9.027262938063792</v>
+        <v>-8.340076447749576</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.311660121145152</v>
       </c>
       <c r="E71">
-        <v>-13.62657434302638</v>
+        <v>-13.51681771850247</v>
       </c>
       <c r="F71">
-        <v>2.565378317788906</v>
+        <v>2.431933299402323</v>
       </c>
       <c r="G71">
-        <v>-8.620466412743689</v>
+        <v>-7.71711454089722</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.268262966542398</v>
       </c>
       <c r="E72">
-        <v>-12.54340411665769</v>
+        <v>-14.12069425589932</v>
       </c>
       <c r="F72">
-        <v>2.411774150287794</v>
+        <v>2.435322978814578</v>
       </c>
       <c r="G72">
-        <v>-7.978657570136262</v>
+        <v>-7.92488106839634</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.18587456686047</v>
       </c>
       <c r="E73">
-        <v>-14.15159203405365</v>
+        <v>-14.24386874890795</v>
       </c>
       <c r="F73">
-        <v>2.296004835542147</v>
+        <v>2.272687949888146</v>
       </c>
       <c r="G73">
-        <v>-8.060408181683025</v>
+        <v>-7.927155413181819</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.068861976918084</v>
       </c>
       <c r="E74">
-        <v>-14.6269414221648</v>
+        <v>-14.35863386568434</v>
       </c>
       <c r="F74">
-        <v>2.410231730183781</v>
+        <v>2.002333680636471</v>
       </c>
       <c r="G74">
-        <v>-8.19897106522922</v>
+        <v>-8.300257206003222</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.91415783072917</v>
       </c>
       <c r="E75">
-        <v>-14.53285784618144</v>
+        <v>-13.62555996484866</v>
       </c>
       <c r="F75">
-        <v>2.178398201897089</v>
+        <v>2.095851390208118</v>
       </c>
       <c r="G75">
-        <v>-7.317498588851794</v>
+        <v>-7.621287489717476</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.723782824825751</v>
       </c>
       <c r="E76">
-        <v>-14.98236323313082</v>
+        <v>-14.04470646205061</v>
       </c>
       <c r="F76">
-        <v>1.980706664484182</v>
+        <v>2.012439762950625</v>
       </c>
       <c r="G76">
-        <v>-7.532789986361679</v>
+        <v>-7.742887137920446</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.498744694342383</v>
       </c>
       <c r="E77">
-        <v>-14.48568926091755</v>
+        <v>-14.85934270823845</v>
       </c>
       <c r="F77">
-        <v>2.140137568296586</v>
+        <v>2.330850938708311</v>
       </c>
       <c r="G77">
-        <v>-7.277609825649116</v>
+        <v>-7.68154603962329</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.236134855966602</v>
       </c>
       <c r="E78">
-        <v>-15.20667666462676</v>
+        <v>-15.21764462867334</v>
       </c>
       <c r="F78">
-        <v>1.972578723527913</v>
+        <v>1.91208139536666</v>
       </c>
       <c r="G78">
-        <v>-7.035168644171669</v>
+        <v>-6.970427615605682</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.940646984539271</v>
       </c>
       <c r="E79">
-        <v>-16.34803325352</v>
+        <v>-15.30792428649026</v>
       </c>
       <c r="F79">
-        <v>1.925605321584764</v>
+        <v>1.792496620363717</v>
       </c>
       <c r="G79">
-        <v>-6.420403648074549</v>
+        <v>-7.003374164812509</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.609850971281172</v>
       </c>
       <c r="E80">
-        <v>-17.19945882254615</v>
+        <v>-16.66680612434194</v>
       </c>
       <c r="F80">
-        <v>1.997585478683624</v>
+        <v>1.995004285856501</v>
       </c>
       <c r="G80">
-        <v>-6.673994746928262</v>
+        <v>-6.787953656026594</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.247651674503723</v>
       </c>
       <c r="E81">
-        <v>-16.91036104189647</v>
+        <v>-17.08151924549038</v>
       </c>
       <c r="F81">
-        <v>1.724840541107471</v>
+        <v>1.874097436478691</v>
       </c>
       <c r="G81">
-        <v>-6.345244332696476</v>
+        <v>-5.524980532794636</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.858945124362623</v>
       </c>
       <c r="E82">
-        <v>-17.74970464227016</v>
+        <v>-18.36150148070642</v>
       </c>
       <c r="F82">
-        <v>1.626551435295698</v>
+        <v>1.826618730419834</v>
       </c>
       <c r="G82">
-        <v>-5.946071993753313</v>
+        <v>-5.972996660624205</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.442942552787035</v>
       </c>
       <c r="E83">
-        <v>-19.03343645396455</v>
+        <v>-19.34043529236655</v>
       </c>
       <c r="F83">
-        <v>2.230719543792712</v>
+        <v>1.961761901982157</v>
       </c>
       <c r="G83">
-        <v>-5.411180529882189</v>
+        <v>-5.819718402155949</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.010957630188686</v>
       </c>
       <c r="E84">
-        <v>-19.98769461075688</v>
+        <v>-19.47758918463686</v>
       </c>
       <c r="F84">
-        <v>1.673069235167307</v>
+        <v>1.867268375610012</v>
       </c>
       <c r="G84">
-        <v>-5.036622097023507</v>
+        <v>-5.287250257619572</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.566950033768738</v>
       </c>
       <c r="E85">
-        <v>-20.6902692391509</v>
+        <v>-20.10408092122801</v>
       </c>
       <c r="F85">
-        <v>1.611493372647608</v>
+        <v>1.886680337327215</v>
       </c>
       <c r="G85">
-        <v>-4.342523187623293</v>
+        <v>-5.271141143025479</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.120447776418453</v>
       </c>
       <c r="E86">
-        <v>-21.83936046164924</v>
+        <v>-22.07616795293235</v>
       </c>
       <c r="F86">
-        <v>1.858867073410819</v>
+        <v>1.846984971385063</v>
       </c>
       <c r="G86">
-        <v>-4.798709741843783</v>
+        <v>-5.127105927702868</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.684598909055505</v>
       </c>
       <c r="E87">
-        <v>-22.83579229687501</v>
+        <v>-22.50946593140827</v>
       </c>
       <c r="F87">
-        <v>1.659803759578876</v>
+        <v>1.961980590976496</v>
       </c>
       <c r="G87">
-        <v>-4.197918558467927</v>
+        <v>-4.15820525417883</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.266759645042296</v>
       </c>
       <c r="E88">
-        <v>-24.31637234520882</v>
+        <v>-23.95217435161594</v>
       </c>
       <c r="F88">
-        <v>1.562677681600634</v>
+        <v>1.64353959399231</v>
       </c>
       <c r="G88">
-        <v>-4.458667056777544</v>
+        <v>-4.189175407698712</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.88433609357885</v>
       </c>
       <c r="E89">
-        <v>-25.2881375825148</v>
+        <v>-26.66581711597232</v>
       </c>
       <c r="F89">
-        <v>1.619538476863597</v>
+        <v>1.382895447436251</v>
       </c>
       <c r="G89">
-        <v>-4.138097000573297</v>
+        <v>-4.29374892019321</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.551882427547159</v>
       </c>
       <c r="E90">
-        <v>-27.76437509701907</v>
+        <v>-26.80175737720858</v>
       </c>
       <c r="F90">
-        <v>1.41529289655974</v>
+        <v>1.457619157373184</v>
       </c>
       <c r="G90">
-        <v>-3.275633676682367</v>
+        <v>-3.61062115871014</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.283114037982733</v>
       </c>
       <c r="E91">
-        <v>-28.62823132719627</v>
+        <v>-28.90682757662216</v>
       </c>
       <c r="F91">
-        <v>1.196057179734823</v>
+        <v>1.000860684939147</v>
       </c>
       <c r="G91">
-        <v>-3.716449367964022</v>
+        <v>-4.02542920423528</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.096126327851493</v>
       </c>
       <c r="E92">
-        <v>-30.36547169686282</v>
+        <v>-31.61282174837959</v>
       </c>
       <c r="F92">
-        <v>0.9701315677648968</v>
+        <v>1.557159097963183</v>
       </c>
       <c r="G92">
-        <v>-3.515178130812952</v>
+        <v>-3.935471750296665</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.003390427839745</v>
       </c>
       <c r="E93">
-        <v>-32.24480878817906</v>
+        <v>-32.47069812862967</v>
       </c>
       <c r="F93">
-        <v>1.317861979377268</v>
+        <v>0.8928482025533142</v>
       </c>
       <c r="G93">
-        <v>-4.123494184199571</v>
+        <v>-4.017311746572988</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.014482591967662</v>
       </c>
       <c r="E94">
-        <v>-34.88702166777545</v>
+        <v>-35.62211526801856</v>
       </c>
       <c r="F94">
-        <v>1.265201006846498</v>
+        <v>0.8132802000448105</v>
       </c>
       <c r="G94">
-        <v>-4.44578572408424</v>
+        <v>-3.912003292968771</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.137776610157651</v>
       </c>
       <c r="E95">
-        <v>-36.16442267280712</v>
+        <v>-37.04069145023935</v>
       </c>
       <c r="F95">
-        <v>1.015466458985308</v>
+        <v>0.7995110770754771</v>
       </c>
       <c r="G95">
-        <v>-4.31941557975918</v>
+        <v>-3.633453991294493</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.374434935439254</v>
       </c>
       <c r="E96">
-        <v>-39.2487074492693</v>
+        <v>-39.35769649744891</v>
       </c>
       <c r="F96">
-        <v>0.6423200787202429</v>
+        <v>0.8979045571800024</v>
       </c>
       <c r="G96">
-        <v>-4.063500477936899</v>
+        <v>-4.927148977130888</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.711773905815289</v>
       </c>
       <c r="E97">
-        <v>-40.90580741442211</v>
+        <v>-41.10884154655601</v>
       </c>
       <c r="F97">
-        <v>0.6757579573016478</v>
+        <v>0.4038148793714036</v>
       </c>
       <c r="G97">
-        <v>-4.850933597725787</v>
+        <v>-4.241081451208945</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.149840050325414</v>
       </c>
       <c r="E98">
-        <v>-44.50885832354398</v>
+        <v>-43.76560214890205</v>
       </c>
       <c r="F98">
-        <v>0.5025281092934095</v>
+        <v>0.2020461176019169</v>
       </c>
       <c r="G98">
-        <v>-4.360426617899671</v>
+        <v>-5.340526866983063</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.647718869003991</v>
       </c>
       <c r="E99">
-        <v>-45.68187573846184</v>
+        <v>-46.70379608963978</v>
       </c>
       <c r="F99">
-        <v>0.2418085813036959</v>
+        <v>0.03687876952512624</v>
       </c>
       <c r="G99">
-        <v>-5.255055202250159</v>
+        <v>-5.184295601893777</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.217523977242433</v>
       </c>
       <c r="E100">
-        <v>-48.46348184072534</v>
+        <v>-48.8461990287726</v>
       </c>
       <c r="F100">
-        <v>-0.1103312299937767</v>
+        <v>-0.007045412008317547</v>
       </c>
       <c r="G100">
-        <v>-5.53009532565281</v>
+        <v>-6.006075631652603</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.786771150667598</v>
       </c>
       <c r="E101">
-        <v>-50.23946556976452</v>
+        <v>-50.21878176473448</v>
       </c>
       <c r="F101">
-        <v>-0.23883172335305</v>
+        <v>-0.2822704815884533</v>
       </c>
       <c r="G101">
-        <v>-5.347422733341365</v>
+        <v>-5.689282907908665</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.415939171026496</v>
       </c>
       <c r="E102">
-        <v>-52.14232015872108</v>
+        <v>-53.09431860698358</v>
       </c>
       <c r="F102">
-        <v>-0.5229360631237937</v>
+        <v>-0.5906211352391385</v>
       </c>
       <c r="G102">
-        <v>-5.975509364688512</v>
+        <v>-5.441134345921514</v>
       </c>
     </row>
   </sheetData>
